--- a/docs/db/raid- statistics.xlsx
+++ b/docs/db/raid- statistics.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\enbu\docs\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71013F1D-A42B-497A-B9DE-DC3CE2AB1D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA0BEBD-E952-48BF-813F-89D94096CF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="history" sheetId="1" r:id="rId1"/>
     <sheet name="第九回妖鬼大討伐" sheetId="2" r:id="rId2"/>
+    <sheet name="第十回妖鬼大討伐" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
   <si>
     <t>攻撃</t>
     <rPh sb="0" eb="2">
@@ -138,6 +139,22 @@
     <rPh sb="6" eb="8">
       <t>トウバツ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第十回妖鬼大討伐</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/2/28</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TA007</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TA014</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -464,9 +481,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
+    <col min="1" max="1" width="16.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.59765625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -476,6 +494,14 @@
       </c>
       <c r="B1" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -641,4 +667,119 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43EA8FF8-578C-4383-BEDE-40D777B105F3}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1">
+        <v>81</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>